--- a/InputData/trans/BCDTRtSY/BAU Cargo Dist Transported Relative to Start Yr.xlsx
+++ b/InputData/trans/BCDTRtSY/BAU Cargo Dist Transported Relative to Start Yr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shigu\Documents\_swj\_Talanoa\CPSA Fletcher\dados\InputData (BR) 2024\d17 trans\BCDTRtSY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/trans/BCDTRtSY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01C255A-E963-452A-9E32-14C72DCDFE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614EB6A7-007C-334E-833F-1689014669A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5508" yWindow="1908" windowWidth="17220" windowHeight="9912" tabRatio="742" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" tabRatio="742" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -288,11 +288,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="###0.00_)"/>
-    <numFmt numFmtId="167" formatCode="#,##0_)"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="###0.00_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="46">
     <font>
@@ -993,33 +993,33 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="8">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="8">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1151,7 +1151,7 @@
     <xf numFmtId="49" fontId="17" fillId="0" borderId="8">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" applyNumberFormat="0">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyNumberFormat="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
@@ -1238,7 +1238,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="154"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1314,7 +1314,7 @@
     <cellStyle name="Hed Top" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
     <cellStyle name="Hed Top - SECTION" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
     <cellStyle name="Hed Top_3-new4" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="Hiperlink" xfId="154" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="154" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="72" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="Input 2" xfId="73" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
     <cellStyle name="Linked Cell 2" xfId="74" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
@@ -1367,12 +1367,12 @@
     <cellStyle name="Output 2" xfId="119" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
     <cellStyle name="Parent row" xfId="3" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
     <cellStyle name="Parent row 2" xfId="120" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="Percent" xfId="153" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="121" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
     <cellStyle name="Percent 2 2" xfId="122" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
     <cellStyle name="Percent 3" xfId="123" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
     <cellStyle name="Percent 3 2" xfId="124" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
     <cellStyle name="Percent 4" xfId="125" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Porcentagem" xfId="153" builtinId="5"/>
     <cellStyle name="Reference" xfId="126" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
     <cellStyle name="Row heading" xfId="127" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
     <cellStyle name="Source Hed" xfId="128" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
@@ -1882,10 +1882,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S65"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="2" width="107.44140625" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="107.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -2062,9 +2062,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AM10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
@@ -2584,9 +2584,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AM10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.109375" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
@@ -3109,12 +3109,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="72">
+    <row r="1" spans="1:33" ht="80">
       <c r="A1" s="23" t="s">
         <v>71</v>
       </c>
@@ -4024,12 +4024,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="72">
+    <row r="1" spans="1:33" ht="80">
       <c r="A1" s="23" t="s">
         <v>71</v>
       </c>
@@ -4139,8 +4139,8 @@
         <v>1</v>
       </c>
       <c r="C2" s="18">
-        <f>INDEX('frgt-Road'!$I12:$I48,COLUMN(E2),1)</f>
-        <v>0</v>
+        <f>B2</f>
+        <v>1</v>
       </c>
       <c r="D2" s="18">
         <f>INDEX('frgt-Road'!$I12:$I48,COLUMN(F2),1)</f>
@@ -4272,8 +4272,8 @@
         <v>1</v>
       </c>
       <c r="C3" s="18">
-        <f>INDEX('frgt-Road'!$J12:$J48,COLUMN(E2),1)</f>
-        <v>0</v>
+        <f>B3</f>
+        <v>1</v>
       </c>
       <c r="D3" s="18">
         <f>INDEX('frgt-Road'!$J12:$J48,COLUMN(F2),1)</f>
@@ -4904,7 +4904,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
@@ -4951,7 +4951,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -4997,11 +4997,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AK31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="51.88671875" customWidth="1"/>
-    <col min="2" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="37" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.83203125" customWidth="1"/>
+    <col min="2" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="37" width="12.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -7723,7 +7723,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AM18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
   </cols>
@@ -8133,9 +8133,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AM21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.109375" customWidth="1"/>
+    <col min="1" max="1" width="38.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
@@ -8662,7 +8662,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AM10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
   </cols>
@@ -9190,15 +9190,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J48"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="44.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -10422,7 +10422,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AM25"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
   </cols>
